--- a/docs/qa/upload-templates/sop_sales_input_upload_template.xlsx
+++ b/docs/qa/upload-templates/sop_sales_input_upload_template.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -463,6 +463,16 @@
           <t>rationale</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>region</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>confidence_pct</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -483,6 +493,14 @@
           <t>Egyptian Electric expansion</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>EG</t>
+        </is>
+      </c>
+      <c r="F2" t="n">
+        <v>80</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -503,6 +521,14 @@
           <t>Saudi program</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>75</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -522,6 +548,14 @@
         <is>
           <t>Tender pipeline</t>
         </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>AE</t>
+        </is>
+      </c>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
